--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487190_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487190_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0831</v>
+        <v>6.5689</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7522</v>
+        <v>6.1309</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3309</v>
+        <v>0.438</v>
       </c>
       <c r="G2" t="n">
         <v>3.7097</v>
@@ -610,13 +610,13 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8196</v>
+        <v>-0.3338</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4132</v>
+        <v>-1.0344</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5935</v>
+        <v>0.7006</v>
       </c>
       <c r="V2" t="n">
         <v>1.842</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7744</v>
+        <v>0.0793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1355</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9099</v>
+        <v>-0.5351</v>
       </c>
       <c r="G3" t="n">
         <v>4.9113</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1765</v>
+        <v>-0.3229</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5176</v>
+        <v>-1.0387</v>
       </c>
       <c r="U3" t="n">
-        <v>0.341</v>
+        <v>0.7158</v>
       </c>
       <c r="V3" t="n">
         <v>-1.228</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8675</v>
+        <v>-0.3936</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1209</v>
+        <v>0.3806</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.7742</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4749</v>
@@ -766,13 +766,13 @@
         <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9716</v>
+        <v>-0.4977</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6253</v>
+        <v>-0.3655</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3464</v>
+        <v>-0.1322</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1137</v>
+        <v>-1.5083</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.127</v>
+        <v>-1.4681</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0134</v>
+        <v>-0.0402</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8995</v>
@@ -844,13 +844,13 @@
         <v>0.193</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5579</v>
+        <v>0.1633</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4442</v>
+        <v>0.1031</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1137</v>
+        <v>0.0601</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4217</v>
+        <v>-1.7925</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6042</v>
+        <v>-1.4664</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1825</v>
+        <v>-0.3261</v>
       </c>
       <c r="G6" t="n">
         <v>-2.1988</v>
@@ -922,13 +922,13 @@
         <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.2776</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3259</v>
+        <v>-1.1881</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4191</v>
+        <v>0.9105</v>
       </c>
       <c r="V6" t="n">
         <v>1.842</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.087</v>
+        <v>-2.2209</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2477</v>
+        <v>-0.4886</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8394</v>
+        <v>-1.7323</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2965</v>
@@ -1000,13 +1000,13 @@
         <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2115</v>
+        <v>-0.3454</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2657</v>
+        <v>0.0248</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4772</v>
+        <v>-0.3702</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.893</v>
+        <v>-2.659</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7885</v>
+        <v>-1.6884</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1045</v>
+        <v>-0.9707</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2858</v>
@@ -1078,13 +1078,13 @@
         <v>0.193</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5493</v>
+        <v>-0.3153</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3113</v>
+        <v>-0.1775</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2859</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5717</v>
+        <v>-3.7855</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.146</v>
+        <v>-1.7077</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4257</v>
+        <v>-2.0777</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5515</v>
@@ -1156,13 +1156,13 @@
         <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6994</v>
+        <v>-0.9132</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.7846</v>
+        <v>-1.3464</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0852</v>
+        <v>0.4332</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5138</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6093</v>
+        <v>-6.3539</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.5386</v>
+        <v>-5.5604</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0707</v>
+        <v>-0.7934</v>
       </c>
       <c r="G10" t="n">
         <v>-6.1936</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6193</v>
+        <v>-0.1253</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1025</v>
+        <v>-1.1243</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7218</v>
+        <v>0.999</v>
       </c>
       <c r="V10" t="n">
         <v>-0.614</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.2552</v>
+        <v>-12.0655</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4434</v>
+        <v>-5.253699999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.8118</v>
+        <v>-6.8117</v>
       </c>
       <c r="G11" t="n">
         <v>-5.279599999999999</v>
@@ -1312,13 +1312,13 @@
         <v>8.6854</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.1575</v>
+        <v>-2.9679</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.297199999999999</v>
+        <v>-6.1073</v>
       </c>
       <c r="U11" t="n">
-        <v>3.1394</v>
+        <v>3.1393</v>
       </c>
       <c r="V11" t="n">
         <v>0.04230000000000012</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. DE LA CRUZ MARTINEZ</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.3237</v>
+        <v>4.5383</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1737</v>
+        <v>3.6559</v>
       </c>
       <c r="F12" t="n">
-        <v>2.15</v>
+        <v>0.8824</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4792</v>
+        <v>1.6103</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3507</v>
+        <v>3.3126</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1285</v>
+        <v>-1.7023</v>
       </c>
       <c r="J12" t="n">
-        <v>2.172</v>
+        <v>3.9644</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4644</v>
+        <v>3.7202</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7076</v>
+        <v>0.2442</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6928</v>
+        <v>-2.3541</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1137</v>
+        <v>-0.4076</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-1.9464</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2076</v>
+        <v>0.6421</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2842</v>
+        <v>-1.1431</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4918</v>
+        <v>1.7853</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2859</v>
+        <v>1.7997</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>G. DE LA CRUZ MARTINEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3179</v>
+        <v>4.4827</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7561</v>
+        <v>2.5743</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5618</v>
+        <v>1.9084</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6103</v>
+        <v>1.4792</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3126</v>
+        <v>1.3507</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7023</v>
+        <v>0.1285</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9644</v>
+        <v>2.172</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7202</v>
+        <v>1.4644</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2442</v>
+        <v>0.7076</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3541</v>
+        <v>-0.6928</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4076</v>
+        <v>-0.1137</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.9464</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4217</v>
+        <v>1.3666</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.043</v>
+        <v>0.1164</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4647</v>
+        <v>1.2502</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7997</v>
+        <v>0.2859</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0026</v>
+        <v>3.4501</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5399</v>
+        <v>2.6401</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4627</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>4.5688</v>
@@ -1546,13 +1546,13 @@
         <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>0.113</v>
+        <v>0.5605</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.162</v>
+        <v>-1.0618</v>
       </c>
       <c r="U14" t="n">
-        <v>1.275</v>
+        <v>1.6223</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3281</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ALLAS MENESES</t>
+          <t>S. MARTINEZ ORTIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.738</v>
+        <v>1.9711</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7030999999999999</v>
+        <v>-0.0285</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0349</v>
+        <v>1.9996</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1359</v>
+        <v>0.9929</v>
       </c>
       <c r="H15" t="n">
-        <v>0.621</v>
+        <v>-0.7443</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7569</v>
+        <v>1.7372</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5709</v>
+        <v>3.0666</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3674</v>
+        <v>-0.7506</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2035</v>
+        <v>3.8172</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7067</v>
+        <v>-2.0736</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2536</v>
+        <v>0.0064</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9604</v>
+        <v>-2.08</v>
       </c>
       <c r="P15" t="n">
-        <v>1.158</v>
+        <v>-0.772</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R15" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7158</v>
+        <v>0.8504</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1322</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5836</v>
+        <v>1.622</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. HERRERO PERAL</t>
+          <t>D. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6059</v>
+        <v>1.4971</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0437</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5622</v>
+        <v>0.794</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2803</v>
+        <v>-0.1359</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9647</v>
+        <v>0.621</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3156</v>
+        <v>-0.7569</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0668</v>
+        <v>0.5709</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8643999999999999</v>
+        <v>0.3674</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7976</v>
+        <v>0.2035</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2135</v>
+        <v>-0.7067</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1003</v>
+        <v>0.2536</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1132</v>
+        <v>-0.9604</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>1.207</v>
+        <v>0.4749</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1105</v>
+        <v>0.1322</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0965</v>
+        <v>0.3427</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>I. HERRERO PERAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4854</v>
+        <v>1.1927</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5809</v>
+        <v>0.0423</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9045</v>
+        <v>1.1504</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5491</v>
+        <v>-1.2803</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0078</v>
+        <v>-0.9647</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4587</v>
+        <v>-0.3156</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0885</v>
+        <v>-0.0668</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7076</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.619</v>
+        <v>0.7976</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5395</v>
+        <v>-1.2135</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3002</v>
+        <v>-0.1003</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8397</v>
+        <v>-1.1132</v>
       </c>
       <c r="P17" t="n">
-        <v>0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0292</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4574</v>
+        <v>0.1091</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5717</v>
+        <v>0.6848</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2859</v>
+        <v>0.3281</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. MARTINEZ ORTIZ</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1102</v>
+        <v>1.0719</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7295</v>
+        <v>-0.0199</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8397</v>
+        <v>1.0918</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9929</v>
+        <v>0.5491</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7443</v>
+        <v>2.0078</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7372</v>
+        <v>-1.4587</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0666</v>
+        <v>1.0885</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7506</v>
+        <v>1.7076</v>
       </c>
       <c r="L18" t="n">
-        <v>3.8172</v>
+        <v>-0.619</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0736</v>
+        <v>-0.5395</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0064</v>
+        <v>0.3002</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.08</v>
+        <v>-0.8397</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0106</v>
+        <v>0.6157</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4726</v>
+        <v>-0.1434</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4621</v>
+        <v>0.7591</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8999</v>
+        <v>-0.2859</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3281</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0883</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.699</v>
+        <v>-0.1983</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7873</v>
+        <v>0.8409</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3334</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3503</v>
+        <v>0.2039</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1785</v>
+        <v>0.3222</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1719</v>
+        <v>-0.1183</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4168</v>
+        <v>-4.2562</v>
       </c>
       <c r="E20" t="n">
         <v>-2.5572</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8596</v>
+        <v>-1.699</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1711</v>
@@ -2014,13 +2014,13 @@
         <v>0.386</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1758</v>
+        <v>-0.0152</v>
       </c>
       <c r="T20" t="n">
         <v>-0.6993</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5235</v>
+        <v>0.6841</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4559</v>
@@ -2047,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>13.2552</v>
+        <v>14.5903</v>
       </c>
       <c r="E21" t="n">
-        <v>6.8117</v>
+        <v>6.8118</v>
       </c>
       <c r="F21" t="n">
-        <v>6.4435</v>
+        <v>7.778500000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>5.2796</v>
+        <v>5.279599999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7085</v>
+        <v>4.708500000000001</v>
       </c>
       <c r="I21" t="n">
         <v>0.5712000000000004</v>
@@ -2080,7 +2080,7 @@
         <v>-0.03519999999999997</v>
       </c>
       <c r="O21" t="n">
-        <v>-9.764400000000002</v>
+        <v>-9.7644</v>
       </c>
       <c r="P21" t="n">
         <v>3.8601</v>
@@ -2092,16 +2092,16 @@
         <v>12.5455</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1576</v>
+        <v>5.4928</v>
       </c>
       <c r="T21" t="n">
-        <v>-3.1395</v>
+        <v>-3.1394</v>
       </c>
       <c r="U21" t="n">
-        <v>7.297000000000001</v>
+        <v>8.632200000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.04220000000000024</v>
+        <v>-0.04219999999999979</v>
       </c>
       <c r="W21" t="n">
         <v>3.5572</v>
